--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J12" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>1</v>
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>158</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.7278481012658228</v>
+        <v>115</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>67</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.01492537313432836</v>
+        <v>1</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         <v>32</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>1</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>50</v>
@@ -941,16 +941,16 @@
         <v>21</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N13" headerRowCount="1">
-  <autoFilter ref="A10:N13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N14" headerRowCount="1">
+  <autoFilter ref="A10:N14"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -910,52 +910,106 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>15621</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>RAVENNA</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>CALIO' ANTONELLA</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>05625</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>247</v>
+        <v>287</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>36</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>36</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>COTIGNOLA</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -875,47 +875,47 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>COTIGNOLA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>50</v>
@@ -1001,10 +1001,10 @@
         <v>1</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,10 +676,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>58</v>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>40</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>3</v>
@@ -903,7 +903,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
         <v>32</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>1</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>50</v>
@@ -1001,10 +1001,10 @@
         <v>1</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR CALIO' ANTONELLA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -875,22 +875,22 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>3</v>
@@ -932,7 +932,7 @@
         <v>32</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>1</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>50</v>
@@ -995,16 +995,16 @@
         <v>21</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
